--- a/BDD_raw/Canada.xlsx
+++ b/BDD_raw/Canada.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canada_Surveys" sheetId="1" r:id="R0710f14df98743d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentation" sheetId="2" r:id="R2d0c445d455e44d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canada_Surveys" sheetId="1" r:id="R2350156b014d4d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentation" sheetId="2" r:id="R513ee5b7e7bf4a08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,9 +14,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
-    <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0.00 &quot;€&quot;"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -55,7 +57,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -98,6 +100,18 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -107,15 +121,11 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="10">
+  <x:dxfs count="5">
     <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF9C0006"/>
-      </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF4CCCC"/>
+          <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -127,13 +137,9 @@
       </x:fill>
     </x:dxf>
     <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF9C0006"/>
-      </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF4CCCC"/>
+          <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -141,53 +147,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF2CC"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF9C0006"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF4CCCC"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF2CC"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF9C0006"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF4CCCC"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF2CC"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF9C0006"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -203,17 +162,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CanadaSurveysTable" displayName="CanadaSurveysTable" ref="A1:I201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CanadaSurveysTable" displayName="CanadaSurveysTable" ref="A1:N201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="survey_id"/>
     <x:tableColumn id="2" name="survey_date"/>
     <x:tableColumn id="3" name="country"/>
     <x:tableColumn id="4" name="product_code"/>
-    <x:tableColumn id="5" name="delivery_time"/>
-    <x:tableColumn id="6" name="delivery_person"/>
-    <x:tableColumn id="7" name="parcel_condition"/>
-    <x:tableColumn id="8" name="customer_service"/>
-    <x:tableColumn id="9" name="overall_satisfaction"/>
+    <x:tableColumn id="5" name="taille_colis"/>
+    <x:tableColumn id="6" name="fragile"/>
+    <x:tableColumn id="7" name="poids_kg"/>
+    <x:tableColumn id="8" name="prix_livraison_eur"/>
+    <x:tableColumn id="9" name="statut_colis"/>
+    <x:tableColumn id="10" name="delivery_time"/>
+    <x:tableColumn id="11" name="delivery_person"/>
+    <x:tableColumn id="12" name="parcel_condition"/>
+    <x:tableColumn id="13" name="customer_service"/>
+    <x:tableColumn id="14" name="overall_satisfaction"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -418,11 +382,16 @@
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -439,18 +408,33 @@
         <x:v>product_code</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
+        <x:v>taille_colis</x:v>
+      </x:c>
+      <x:c r="F1" s="10" t="str">
+        <x:v>fragile</x:v>
+      </x:c>
+      <x:c r="G1" s="10" t="str">
+        <x:v>poids_kg</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="str">
+        <x:v>prix_livraison_eur</x:v>
+      </x:c>
+      <x:c r="I1" s="10" t="str">
+        <x:v>statut_colis</x:v>
+      </x:c>
+      <x:c r="J1" s="10" t="str">
         <x:v>delivery_time</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="K1" s="10" t="str">
         <x:v>delivery_person</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
+      <x:c r="L1" s="10" t="str">
         <x:v>parcel_condition</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
+      <x:c r="M1" s="10" t="str">
         <x:v>customer_service</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
+      <x:c r="N1" s="10" t="str">
         <x:v>overall_satisfaction</x:v>
       </x:c>
     </x:row>
@@ -467,19 +451,34 @@
       <x:c r="D2" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E2" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="16" t="n">
+      <x:c r="E2" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="H2" s="18" t="n">
+        <x:v>18.88</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J2" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K2" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H2" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I2" s="16"/>
+      <x:c r="L2" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M2" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N2" s="20"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -494,19 +493,34 @@
       <x:c r="D3" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E3" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G3" s="16" t="n">
+        <x:v>1.26</x:v>
+      </x:c>
+      <x:c r="H3" s="18" t="n">
+        <x:v>6.56</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J3" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L3" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H3" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I3" s="16" t="n">
+      <x:c r="M3" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N3" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -523,17 +537,32 @@
       <x:c r="D4" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="n">
+      <x:c r="E4" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="H4" s="18" t="n">
+        <x:v>6.21</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="n">
+      <x:c r="L4" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H4" s="16"/>
-      <x:c r="I4" s="16" t="n">
+      <x:c r="M4" s="20"/>
+      <x:c r="N4" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -550,17 +579,32 @@
       <x:c r="D5" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F5" s="16"/>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G5" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="16" t="n">
+        <x:v>14.1</x:v>
+      </x:c>
+      <x:c r="H5" s="18" t="n">
+        <x:v>15.29</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K5" s="20"/>
+      <x:c r="L5" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M5" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N5" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -577,17 +621,32 @@
       <x:c r="D6" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G6" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="16"/>
-      <x:c r="I6" s="16" t="n">
+        <x:v>2.42</x:v>
+      </x:c>
+      <x:c r="H6" s="18" t="n">
+        <x:v>10.1</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J6" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L6" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M6" s="20"/>
+      <x:c r="N6" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -604,19 +663,34 @@
       <x:c r="D7" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="n">
+      <x:c r="E7" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="n">
+        <x:v>0.84</x:v>
+      </x:c>
+      <x:c r="H7" s="18" t="n">
+        <x:v>6.27</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J7" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H7" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="K7" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L7" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M7" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N7" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -633,19 +707,34 @@
       <x:c r="D8" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E8" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F8" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G8" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H8" s="16" t="n">
+        <x:v>0.91</x:v>
+      </x:c>
+      <x:c r="H8" s="18" t="n">
+        <x:v>6.32</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J8" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K8" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L8" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M8" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="n">
+      <x:c r="N8" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -662,19 +751,34 @@
       <x:c r="D9" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E9" s="16" t="n">
+      <x:c r="E9" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="n">
+        <x:v>4.86</x:v>
+      </x:c>
+      <x:c r="H9" s="18" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J9" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F9" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G9" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H9" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="K9" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L9" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M9" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N9" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -691,19 +795,34 @@
       <x:c r="D10" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="n">
+      <x:c r="E10" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="H10" s="18" t="n">
+        <x:v>8.52</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J10" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H10" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="K10" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L10" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M10" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N10" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -720,19 +839,34 @@
       <x:c r="D11" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G11" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H11" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I11" s="16" t="n">
+        <x:v>1.23</x:v>
+      </x:c>
+      <x:c r="H11" s="18" t="n">
+        <x:v>6.54</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J11" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L11" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M11" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N11" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -749,17 +883,32 @@
       <x:c r="D12" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G12" s="16"/>
-      <x:c r="H12" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I12" s="16" t="n">
+      <x:c r="E12" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="n">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="H12" s="18" t="n">
+        <x:v>8.25</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J12" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L12" s="20"/>
+      <x:c r="M12" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N12" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -776,19 +925,34 @@
       <x:c r="D13" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E13" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G13" s="16" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="H13" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I13" s="16" t="n">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="H13" s="18" t="n">
+        <x:v>5.85</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J13" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L13" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M13" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N13" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -805,19 +969,34 @@
       <x:c r="D14" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="n">
+      <x:c r="E14" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="n">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H14" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J14" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G14" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H14" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I14" s="16" t="n">
+      <x:c r="L14" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M14" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N14" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -834,19 +1013,34 @@
       <x:c r="D15" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E15" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G15" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H15" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I15" s="16" t="n">
+        <x:v>8.09</x:v>
+      </x:c>
+      <x:c r="H15" s="18" t="n">
+        <x:v>13.95</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J15" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L15" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M15" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N15" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -863,19 +1057,34 @@
       <x:c r="D16" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="n">
+      <x:c r="E16" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="H16" s="18" t="n">
+        <x:v>6.69</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J16" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F16" s="16" t="n">
+      <x:c r="K16" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G16" s="16" t="n">
+      <x:c r="L16" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="n">
+      <x:c r="M16" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="n">
+      <x:c r="N16" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -892,19 +1101,34 @@
       <x:c r="D17" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E17" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G17" s="16" t="n">
+        <x:v>0.87</x:v>
+      </x:c>
+      <x:c r="H17" s="18" t="n">
+        <x:v>6.29</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J17" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L17" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I17" s="16" t="n">
+      <x:c r="M17" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N17" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -921,19 +1145,34 @@
       <x:c r="D18" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="n">
+      <x:c r="E18" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="n">
+        <x:v>2.27</x:v>
+      </x:c>
+      <x:c r="H18" s="18" t="n">
+        <x:v>7.24</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J18" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F18" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H18" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I18" s="16" t="n">
+      <x:c r="K18" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L18" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M18" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N18" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -950,19 +1189,34 @@
       <x:c r="D19" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E19" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="n">
+      <x:c r="E19" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="n">
+        <x:v>11.19</x:v>
+      </x:c>
+      <x:c r="H19" s="18" t="n">
+        <x:v>23.41</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J19" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G19" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H19" s="16" t="n">
+      <x:c r="L19" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M19" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I19" s="16" t="n">
+      <x:c r="N19" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -979,19 +1233,34 @@
       <x:c r="D20" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E20" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E20" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H20" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I20" s="16" t="n">
+        <x:v>5.56</x:v>
+      </x:c>
+      <x:c r="H20" s="18" t="n">
+        <x:v>13.68</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J20" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L20" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M20" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N20" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -1008,17 +1277,32 @@
       <x:c r="D21" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E21" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F21" s="16"/>
+      <x:c r="E21" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G21" s="16" t="n">
+        <x:v>2.06</x:v>
+      </x:c>
+      <x:c r="H21" s="18" t="n">
+        <x:v>7.1</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J21" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K21" s="20"/>
+      <x:c r="L21" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H21" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I21" s="16"/>
+      <x:c r="M21" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N21" s="20"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -1033,19 +1317,34 @@
       <x:c r="D22" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E22" s="16" t="n">
+      <x:c r="E22" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="n">
+        <x:v>5.72</x:v>
+      </x:c>
+      <x:c r="H22" s="18" t="n">
+        <x:v>16.54</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J22" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F22" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H22" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I22" s="16" t="n">
+      <x:c r="K22" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L22" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M22" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N22" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -1062,19 +1361,34 @@
       <x:c r="D23" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E23" s="16" t="n">
+      <x:c r="E23" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="n">
+        <x:v>9.18</x:v>
+      </x:c>
+      <x:c r="H23" s="18" t="n">
+        <x:v>16.14</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J23" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F23" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H23" s="16" t="n">
+      <x:c r="K23" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L23" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M23" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I23" s="16" t="n">
+      <x:c r="N23" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1091,19 +1405,34 @@
       <x:c r="D24" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E24" s="16" t="n">
+      <x:c r="E24" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="H24" s="18" t="n">
+        <x:v>5.95</x:v>
+      </x:c>
+      <x:c r="I24" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J24" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F24" s="16" t="n">
+      <x:c r="K24" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G24" s="16" t="n">
+      <x:c r="L24" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H24" s="16" t="n">
+      <x:c r="M24" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I24" s="16" t="n">
+      <x:c r="N24" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -1120,19 +1449,34 @@
       <x:c r="D25" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E25" s="16" t="n">
+      <x:c r="E25" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="n">
+        <x:v>7.14</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="n">
+        <x:v>10.56</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J25" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F25" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H25" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I25" s="16" t="n">
+      <x:c r="K25" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L25" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M25" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N25" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1149,19 +1493,34 @@
       <x:c r="D26" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E26" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F26" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E26" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H26" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I26" s="16" t="n">
+        <x:v>1.28</x:v>
+      </x:c>
+      <x:c r="H26" s="18" t="n">
+        <x:v>6.57</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J26" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L26" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M26" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N26" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1178,19 +1537,34 @@
       <x:c r="D27" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E27" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F27" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E27" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H27" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I27" s="16" t="n">
+        <x:v>3.13</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="n">
+        <x:v>14.78</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J27" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L27" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M27" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N27" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1207,17 +1581,32 @@
       <x:c r="D28" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E28" s="16" t="n">
+      <x:c r="E28" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="H28" s="18" t="n">
+        <x:v>7.54</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J28" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F28" s="16" t="n">
+      <x:c r="K28" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G28" s="16"/>
-      <x:c r="H28" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I28" s="16" t="n">
+      <x:c r="L28" s="20"/>
+      <x:c r="M28" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N28" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1234,19 +1623,34 @@
       <x:c r="D29" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E29" s="16" t="n">
+      <x:c r="E29" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="n">
+        <x:v>1.44</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="n">
+        <x:v>6.68</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J29" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F29" s="16" t="n">
+      <x:c r="K29" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G29" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H29" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I29" s="16" t="n">
+      <x:c r="L29" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M29" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N29" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1263,19 +1667,34 @@
       <x:c r="D30" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E30" s="16" t="n">
+      <x:c r="E30" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="n">
+        <x:v>2.56</x:v>
+      </x:c>
+      <x:c r="H30" s="18" t="n">
+        <x:v>20.29</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J30" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F30" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H30" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I30" s="16" t="n">
+      <x:c r="K30" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L30" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M30" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N30" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1292,19 +1711,34 @@
       <x:c r="D31" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E31" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F31" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E31" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G31" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H31" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I31" s="16"/>
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H31" s="18" t="n">
+        <x:v>5.99</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J31" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L31" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M31" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N31" s="20"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
@@ -1319,19 +1753,34 @@
       <x:c r="D32" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E32" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F32" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E32" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G32" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H32" s="16" t="n">
+        <x:v>4.52</x:v>
+      </x:c>
+      <x:c r="H32" s="18" t="n">
+        <x:v>18.87</x:v>
+      </x:c>
+      <x:c r="I32" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J32" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L32" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M32" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I32" s="16" t="n">
+      <x:c r="N32" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1348,19 +1797,34 @@
       <x:c r="D33" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E33" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F33" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E33" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
+        <x:v>1.76</x:v>
+      </x:c>
+      <x:c r="H33" s="18" t="n">
+        <x:v>9.65</x:v>
+      </x:c>
+      <x:c r="I33" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J33" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L33" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H33" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I33" s="16"/>
+      <x:c r="M33" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N33" s="20"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
@@ -1375,19 +1839,34 @@
       <x:c r="D34" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E34" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F34" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E34" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G34" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H34" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I34" s="16"/>
+        <x:v>16.31</x:v>
+      </x:c>
+      <x:c r="H34" s="18" t="n">
+        <x:v>19.54</x:v>
+      </x:c>
+      <x:c r="I34" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J34" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L34" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M34" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N34" s="20"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="11" t="str">
@@ -1402,19 +1881,34 @@
       <x:c r="D35" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E35" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F35" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E35" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G35" s="16" t="n">
+        <x:v>2.06</x:v>
+      </x:c>
+      <x:c r="H35" s="18" t="n">
+        <x:v>14.05</x:v>
+      </x:c>
+      <x:c r="I35" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J35" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L35" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H35" s="16" t="n">
+      <x:c r="M35" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I35" s="16" t="n">
+      <x:c r="N35" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1431,19 +1925,34 @@
       <x:c r="D36" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E36" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F36" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E36" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G36" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H36" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I36" s="16" t="n">
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="H36" s="18" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I36" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J36" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L36" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M36" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N36" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1460,19 +1969,34 @@
       <x:c r="D37" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E37" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F37" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E37" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G37" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H37" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I37" s="16" t="n">
+        <x:v>5.41</x:v>
+      </x:c>
+      <x:c r="H37" s="18" t="n">
+        <x:v>9.38</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J37" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L37" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M37" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N37" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -1489,19 +2013,34 @@
       <x:c r="D38" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E38" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F38" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E38" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G38" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H38" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I38" s="16" t="n">
+        <x:v>1.76</x:v>
+      </x:c>
+      <x:c r="H38" s="18" t="n">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="I38" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J38" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L38" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M38" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N38" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1518,17 +2057,32 @@
       <x:c r="D39" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E39" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F39" s="16"/>
+      <x:c r="E39" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="G39" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H39" s="16" t="n">
+        <x:v>2.81</x:v>
+      </x:c>
+      <x:c r="H39" s="18" t="n">
+        <x:v>14.56</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J39" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K39" s="20"/>
+      <x:c r="L39" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M39" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I39" s="16" t="n">
+      <x:c r="N39" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1545,19 +2099,34 @@
       <x:c r="D40" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E40" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F40" s="16" t="n">
+      <x:c r="E40" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="n">
+        <x:v>1.14</x:v>
+      </x:c>
+      <x:c r="H40" s="18" t="n">
+        <x:v>16.58</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J40" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G40" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H40" s="16" t="n">
+      <x:c r="L40" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M40" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I40" s="16" t="n">
+      <x:c r="N40" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1574,19 +2143,34 @@
       <x:c r="D41" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E41" s="16" t="n">
+      <x:c r="E41" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="n">
+        <x:v>5.91</x:v>
+      </x:c>
+      <x:c r="H41" s="18" t="n">
+        <x:v>9.72</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J41" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F41" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G41" s="16" t="n">
+      <x:c r="K41" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L41" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H41" s="16" t="n">
+      <x:c r="M41" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I41" s="16" t="n">
+      <x:c r="N41" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1603,19 +2187,34 @@
       <x:c r="D42" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E42" s="16" t="n">
+      <x:c r="E42" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="n">
+        <x:v>12.96</x:v>
+      </x:c>
+      <x:c r="H42" s="18" t="n">
+        <x:v>14.51</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J42" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F42" s="16" t="n">
+      <x:c r="K42" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G42" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H42" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I42" s="16" t="n">
+      <x:c r="L42" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M42" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N42" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1632,19 +2231,34 @@
       <x:c r="D43" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E43" s="16" t="n">
+      <x:c r="E43" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="n">
+        <x:v>3.64</x:v>
+      </x:c>
+      <x:c r="H43" s="18" t="n">
+        <x:v>8.18</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J43" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F43" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G43" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H43" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I43" s="16" t="n">
+      <x:c r="K43" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L43" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M43" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N43" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1661,19 +2275,34 @@
       <x:c r="D44" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E44" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F44" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E44" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G44" s="16" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="H44" s="18" t="n">
+        <x:v>6.69</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J44" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K44" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L44" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H44" s="16" t="n">
+      <x:c r="M44" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I44" s="16" t="n">
+      <x:c r="N44" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1690,19 +2319,34 @@
       <x:c r="D45" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E45" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F45" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E45" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G45" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H45" s="16" t="n">
+        <x:v>5.84</x:v>
+      </x:c>
+      <x:c r="H45" s="18" t="n">
+        <x:v>19.77</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J45" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K45" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L45" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M45" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I45" s="16" t="n">
+      <x:c r="N45" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1719,19 +2363,34 @@
       <x:c r="D46" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E46" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F46" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E46" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G46" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H46" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I46" s="16" t="n">
+        <x:v>2.86</x:v>
+      </x:c>
+      <x:c r="H46" s="18" t="n">
+        <x:v>10.39</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J46" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K46" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L46" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M46" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N46" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1748,17 +2407,32 @@
       <x:c r="D47" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E47" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F47" s="16" t="n">
+      <x:c r="E47" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H47" s="18" t="n">
+        <x:v>10.27</x:v>
+      </x:c>
+      <x:c r="I47" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J47" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K47" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G47" s="16"/>
-      <x:c r="H47" s="16" t="n">
+      <x:c r="L47" s="20"/>
+      <x:c r="M47" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I47" s="16" t="n">
+      <x:c r="N47" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1775,19 +2449,34 @@
       <x:c r="D48" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E48" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F48" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E48" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G48" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H48" s="16" t="n">
+        <x:v>11.22</x:v>
+      </x:c>
+      <x:c r="H48" s="18" t="n">
+        <x:v>20.28</x:v>
+      </x:c>
+      <x:c r="I48" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J48" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K48" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L48" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M48" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I48" s="16" t="n">
+      <x:c r="N48" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1804,19 +2493,34 @@
       <x:c r="D49" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E49" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F49" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E49" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G49" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H49" s="16" t="n">
+        <x:v>14.49</x:v>
+      </x:c>
+      <x:c r="H49" s="18" t="n">
+        <x:v>15.55</x:v>
+      </x:c>
+      <x:c r="I49" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J49" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K49" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L49" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M49" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I49" s="16" t="n">
+      <x:c r="N49" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -1833,17 +2537,32 @@
       <x:c r="D50" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E50" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F50" s="16"/>
+      <x:c r="E50" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G50" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H50" s="16" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="H50" s="18" t="n">
+        <x:v>7.85</x:v>
+      </x:c>
+      <x:c r="I50" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J50" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K50" s="20"/>
+      <x:c r="L50" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M50" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I50" s="16" t="n">
+      <x:c r="N50" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1860,19 +2579,34 @@
       <x:c r="D51" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E51" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F51" s="16" t="n">
+      <x:c r="E51" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G51" s="16" t="n">
+        <x:v>5.59</x:v>
+      </x:c>
+      <x:c r="H51" s="18" t="n">
+        <x:v>13.7</x:v>
+      </x:c>
+      <x:c r="I51" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J51" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K51" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G51" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H51" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I51" s="16" t="n">
+      <x:c r="L51" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M51" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N51" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1889,19 +2623,34 @@
       <x:c r="D52" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E52" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F52" s="16" t="n">
+      <x:c r="E52" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="n">
+        <x:v>0.62</x:v>
+      </x:c>
+      <x:c r="H52" s="18" t="n">
+        <x:v>6.12</x:v>
+      </x:c>
+      <x:c r="I52" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J52" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K52" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G52" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H52" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I52" s="16" t="n">
+      <x:c r="L52" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M52" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N52" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1918,19 +2667,34 @@
       <x:c r="D53" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E53" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F53" s="16" t="n">
+      <x:c r="E53" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="n">
+        <x:v>3.78</x:v>
+      </x:c>
+      <x:c r="H53" s="18" t="n">
+        <x:v>11.02</x:v>
+      </x:c>
+      <x:c r="I53" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J53" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K53" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G53" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H53" s="16" t="n">
+      <x:c r="L53" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M53" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I53" s="16" t="n">
+      <x:c r="N53" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1947,19 +2711,34 @@
       <x:c r="D54" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E54" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F54" s="16" t="n">
+      <x:c r="E54" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H54" s="18" t="n">
+        <x:v>6.24</x:v>
+      </x:c>
+      <x:c r="I54" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J54" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K54" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G54" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H54" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I54" s="16" t="n">
+      <x:c r="L54" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M54" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N54" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -1976,19 +2755,34 @@
       <x:c r="D55" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E55" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F55" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E55" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G55" s="16" t="n">
+        <x:v>5.28</x:v>
+      </x:c>
+      <x:c r="H55" s="18" t="n">
+        <x:v>9.29</x:v>
+      </x:c>
+      <x:c r="I55" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J55" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K55" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L55" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H55" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I55" s="16" t="n">
+      <x:c r="M55" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N55" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -2005,17 +2799,32 @@
       <x:c r="D56" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E56" s="16" t="n">
+      <x:c r="E56" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="n">
+        <x:v>5.28</x:v>
+      </x:c>
+      <x:c r="H56" s="18" t="n">
+        <x:v>19.39</x:v>
+      </x:c>
+      <x:c r="I56" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J56" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F56" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G56" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H56" s="16"/>
-      <x:c r="I56" s="16" t="n">
+      <x:c r="K56" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L56" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M56" s="20"/>
+      <x:c r="N56" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2032,19 +2841,34 @@
       <x:c r="D57" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E57" s="16" t="n">
+      <x:c r="E57" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="n">
+        <x:v>1.86</x:v>
+      </x:c>
+      <x:c r="H57" s="18" t="n">
+        <x:v>11.16</x:v>
+      </x:c>
+      <x:c r="I57" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J57" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F57" s="16" t="n">
+      <x:c r="K57" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G57" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H57" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I57" s="16" t="n">
+      <x:c r="L57" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M57" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N57" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2061,19 +2885,34 @@
       <x:c r="D58" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E58" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F58" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E58" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F58" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G58" s="16" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H58" s="18" t="n">
+        <x:v>6.86</x:v>
+      </x:c>
+      <x:c r="I58" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J58" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K58" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L58" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H58" s="16" t="n">
+      <x:c r="M58" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I58" s="16" t="n">
+      <x:c r="N58" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2090,19 +2929,34 @@
       <x:c r="D59" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E59" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F59" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E59" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G59" s="16" t="n">
+        <x:v>3.07</x:v>
+      </x:c>
+      <x:c r="H59" s="18" t="n">
+        <x:v>10.54</x:v>
+      </x:c>
+      <x:c r="I59" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J59" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K59" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L59" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H59" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I59" s="16" t="n">
+      <x:c r="M59" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N59" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2119,19 +2973,34 @@
       <x:c r="D60" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E60" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F60" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E60" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F60" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G60" s="16" t="n">
+        <x:v>4.69</x:v>
+      </x:c>
+      <x:c r="H60" s="18" t="n">
+        <x:v>21.74</x:v>
+      </x:c>
+      <x:c r="I60" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J60" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K60" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L60" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H60" s="16" t="n">
+      <x:c r="M60" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I60" s="16" t="n">
+      <x:c r="N60" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -2148,17 +3017,32 @@
       <x:c r="D61" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E61" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F61" s="16"/>
+      <x:c r="E61" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G61" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H61" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I61" s="16" t="n">
+        <x:v>8.65</x:v>
+      </x:c>
+      <x:c r="H61" s="18" t="n">
+        <x:v>11.58</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J61" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K61" s="20"/>
+      <x:c r="L61" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M61" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N61" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2175,19 +3059,34 @@
       <x:c r="D62" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E62" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F62" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E62" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G62" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H62" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I62" s="16" t="n">
+        <x:v>7.78</x:v>
+      </x:c>
+      <x:c r="H62" s="18" t="n">
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J62" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K62" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L62" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M62" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N62" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2204,17 +3103,32 @@
       <x:c r="D63" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E63" s="16"/>
-      <x:c r="F63" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E63" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G63" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H63" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I63" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H63" s="18" t="n">
+        <x:v>6.38</x:v>
+      </x:c>
+      <x:c r="I63" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J63" s="20"/>
+      <x:c r="K63" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L63" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M63" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N63" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2231,19 +3145,34 @@
       <x:c r="D64" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E64" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F64" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E64" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G64" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H64" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I64" s="16" t="n">
+        <x:v>8.3</x:v>
+      </x:c>
+      <x:c r="H64" s="18" t="n">
+        <x:v>21.44</x:v>
+      </x:c>
+      <x:c r="I64" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J64" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K64" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L64" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M64" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N64" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2260,19 +3189,34 @@
       <x:c r="D65" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E65" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F65" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E65" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G65" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H65" s="16" t="n">
+        <x:v>5.91</x:v>
+      </x:c>
+      <x:c r="H65" s="18" t="n">
+        <x:v>13.92</x:v>
+      </x:c>
+      <x:c r="I65" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J65" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K65" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L65" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M65" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I65" s="16" t="n">
+      <x:c r="N65" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2289,19 +3233,34 @@
       <x:c r="D66" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E66" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F66" s="16" t="n">
+      <x:c r="E66" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G66" s="16" t="n">
+        <x:v>13.19</x:v>
+      </x:c>
+      <x:c r="H66" s="18" t="n">
+        <x:v>27.52</x:v>
+      </x:c>
+      <x:c r="I66" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J66" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K66" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G66" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H66" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I66" s="16" t="n">
+      <x:c r="L66" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M66" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N66" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -2318,19 +3277,34 @@
       <x:c r="D67" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E67" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F67" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E67" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G67" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H67" s="18" t="n">
+        <x:v>10.58</x:v>
+      </x:c>
+      <x:c r="I67" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J67" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K67" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L67" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H67" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I67" s="16" t="n">
+      <x:c r="M67" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N67" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2347,15 +3321,30 @@
       <x:c r="D68" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E68" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F68" s="16"/>
+      <x:c r="E68" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G68" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H68" s="16"/>
-      <x:c r="I68" s="16" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="H68" s="18" t="n">
+        <x:v>8.69</x:v>
+      </x:c>
+      <x:c r="I68" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J68" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K68" s="20"/>
+      <x:c r="L68" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M68" s="20"/>
+      <x:c r="N68" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2372,19 +3361,34 @@
       <x:c r="D69" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E69" s="16" t="n">
+      <x:c r="E69" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G69" s="16" t="n">
+        <x:v>2.34</x:v>
+      </x:c>
+      <x:c r="H69" s="18" t="n">
+        <x:v>11.49</x:v>
+      </x:c>
+      <x:c r="I69" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J69" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F69" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G69" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H69" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I69" s="16" t="n">
+      <x:c r="K69" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L69" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M69" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N69" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -2401,19 +3405,34 @@
       <x:c r="D70" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E70" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F70" s="16" t="n">
+      <x:c r="E70" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G70" s="16" t="n">
+        <x:v>3.71</x:v>
+      </x:c>
+      <x:c r="H70" s="18" t="n">
+        <x:v>8.22</x:v>
+      </x:c>
+      <x:c r="I70" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J70" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K70" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G70" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H70" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I70" s="16" t="n">
+      <x:c r="L70" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M70" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N70" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2430,19 +3449,34 @@
       <x:c r="D71" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E71" s="16" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F71" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E71" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G71" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H71" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I71" s="16" t="n">
+        <x:v>1.16</x:v>
+      </x:c>
+      <x:c r="H71" s="18" t="n">
+        <x:v>9.24</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J71" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K71" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L71" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M71" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N71" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2459,19 +3493,34 @@
       <x:c r="D72" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E72" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F72" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E72" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F72" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G72" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H72" s="16" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="H72" s="18" t="n">
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="I72" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J72" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K72" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L72" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M72" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I72" s="16" t="n">
+      <x:c r="N72" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -2488,19 +3537,34 @@
       <x:c r="D73" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E73" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F73" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E73" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G73" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H73" s="16" t="n">
+        <x:v>10.95</x:v>
+      </x:c>
+      <x:c r="H73" s="18" t="n">
+        <x:v>13.15</x:v>
+      </x:c>
+      <x:c r="I73" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J73" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K73" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L73" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M73" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I73" s="16" t="n">
+      <x:c r="N73" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2517,19 +3581,34 @@
       <x:c r="D74" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E74" s="16" t="n">
+      <x:c r="E74" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F74" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G74" s="16" t="n">
+        <x:v>4.19</x:v>
+      </x:c>
+      <x:c r="H74" s="18" t="n">
+        <x:v>8.55</x:v>
+      </x:c>
+      <x:c r="I74" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J74" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F74" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G74" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H74" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I74" s="16" t="n">
+      <x:c r="K74" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L74" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M74" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N74" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2546,19 +3625,34 @@
       <x:c r="D75" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E75" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F75" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E75" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F75" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G75" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H75" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I75" s="16" t="n">
+        <x:v>15.34</x:v>
+      </x:c>
+      <x:c r="H75" s="18" t="n">
+        <x:v>20.33</x:v>
+      </x:c>
+      <x:c r="I75" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J75" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K75" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L75" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M75" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N75" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -2575,19 +3669,34 @@
       <x:c r="D76" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E76" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F76" s="16" t="n">
+      <x:c r="E76" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F76" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G76" s="16" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="H76" s="18" t="n">
+        <x:v>13.57</x:v>
+      </x:c>
+      <x:c r="I76" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J76" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K76" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G76" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H76" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I76" s="16" t="n">
+      <x:c r="L76" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M76" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N76" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2604,17 +3713,32 @@
       <x:c r="D77" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E77" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F77" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G77" s="16"/>
-      <x:c r="H77" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I77" s="16" t="n">
+      <x:c r="E77" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G77" s="16" t="n">
+        <x:v>7.09</x:v>
+      </x:c>
+      <x:c r="H77" s="18" t="n">
+        <x:v>20.62</x:v>
+      </x:c>
+      <x:c r="I77" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J77" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K77" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L77" s="20"/>
+      <x:c r="M77" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N77" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2631,19 +3755,34 @@
       <x:c r="D78" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E78" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F78" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E78" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F78" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G78" s="16" t="n">
+        <x:v>6.15</x:v>
+      </x:c>
+      <x:c r="H78" s="18" t="n">
+        <x:v>14.08</x:v>
+      </x:c>
+      <x:c r="I78" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J78" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K78" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L78" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H78" s="16" t="n">
+      <x:c r="M78" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I78" s="16" t="n">
+      <x:c r="N78" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2660,19 +3799,34 @@
       <x:c r="D79" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E79" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F79" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E79" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F79" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G79" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H79" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I79" s="16" t="n">
+        <x:v>4.45</x:v>
+      </x:c>
+      <x:c r="H79" s="18" t="n">
+        <x:v>8.73</x:v>
+      </x:c>
+      <x:c r="I79" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J79" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K79" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L79" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M79" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N79" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2689,19 +3843,34 @@
       <x:c r="D80" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E80" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F80" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E80" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G80" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H80" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I80" s="16" t="n">
+        <x:v>1.48</x:v>
+      </x:c>
+      <x:c r="H80" s="18" t="n">
+        <x:v>6.71</x:v>
+      </x:c>
+      <x:c r="I80" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J80" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K80" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L80" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M80" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N80" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2718,19 +3887,34 @@
       <x:c r="D81" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E81" s="16" t="n">
+      <x:c r="E81" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G81" s="16" t="n">
+        <x:v>8.21</x:v>
+      </x:c>
+      <x:c r="H81" s="18" t="n">
+        <x:v>11.28</x:v>
+      </x:c>
+      <x:c r="I81" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J81" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F81" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G81" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H81" s="16" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I81" s="16" t="n">
+      <x:c r="K81" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L81" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M81" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N81" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2747,19 +3931,34 @@
       <x:c r="D82" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E82" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F82" s="16" t="n">
+      <x:c r="E82" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F82" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G82" s="16" t="n">
+        <x:v>4.24</x:v>
+      </x:c>
+      <x:c r="H82" s="18" t="n">
+        <x:v>8.58</x:v>
+      </x:c>
+      <x:c r="I82" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J82" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K82" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G82" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H82" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I82" s="16" t="n">
+      <x:c r="L82" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M82" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N82" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2776,17 +3975,32 @@
       <x:c r="D83" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E83" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F83" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E83" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G83" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H83" s="16"/>
-      <x:c r="I83" s="16" t="n">
+        <x:v>8.16</x:v>
+      </x:c>
+      <x:c r="H83" s="18" t="n">
+        <x:v>11.25</x:v>
+      </x:c>
+      <x:c r="I83" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J83" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K83" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L83" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M83" s="20"/>
+      <x:c r="N83" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2803,19 +4017,34 @@
       <x:c r="D84" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E84" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F84" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E84" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F84" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G84" s="16" t="n">
+        <x:v>4.89</x:v>
+      </x:c>
+      <x:c r="H84" s="18" t="n">
+        <x:v>15.98</x:v>
+      </x:c>
+      <x:c r="I84" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J84" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K84" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L84" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H84" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I84" s="16" t="n">
+      <x:c r="M84" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N84" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2832,19 +4061,34 @@
       <x:c r="D85" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E85" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F85" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E85" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G85" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H85" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I85" s="16" t="n">
+        <x:v>3.55</x:v>
+      </x:c>
+      <x:c r="H85" s="18" t="n">
+        <x:v>8.11</x:v>
+      </x:c>
+      <x:c r="I85" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J85" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K85" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L85" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M85" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N85" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2861,19 +4105,34 @@
       <x:c r="D86" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E86" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F86" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E86" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F86" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G86" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H86" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I86" s="16" t="n">
+        <x:v>2.04</x:v>
+      </x:c>
+      <x:c r="H86" s="18" t="n">
+        <x:v>11.29</x:v>
+      </x:c>
+      <x:c r="I86" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J86" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K86" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L86" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M86" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N86" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2890,19 +4149,34 @@
       <x:c r="D87" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E87" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F87" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E87" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G87" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H87" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I87" s="16" t="n">
+        <x:v>4.45</x:v>
+      </x:c>
+      <x:c r="H87" s="18" t="n">
+        <x:v>12.93</x:v>
+      </x:c>
+      <x:c r="I87" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J87" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K87" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L87" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M87" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N87" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2919,19 +4193,34 @@
       <x:c r="D88" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E88" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F88" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E88" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G88" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H88" s="16" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H88" s="18" t="n">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="I88" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J88" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K88" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L88" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M88" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I88" s="16" t="n">
+      <x:c r="N88" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -2948,19 +4237,34 @@
       <x:c r="D89" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E89" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F89" s="16" t="n">
+      <x:c r="E89" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G89" s="16" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H89" s="18" t="n">
+        <x:v>6.08</x:v>
+      </x:c>
+      <x:c r="I89" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J89" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K89" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G89" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H89" s="16" t="n">
+      <x:c r="L89" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M89" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I89" s="16" t="n">
+      <x:c r="N89" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2977,19 +4281,34 @@
       <x:c r="D90" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E90" s="16" t="n">
+      <x:c r="E90" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F90" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G90" s="16" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="H90" s="18" t="n">
+        <x:v>8.37</x:v>
+      </x:c>
+      <x:c r="I90" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J90" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F90" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G90" s="16" t="n">
+      <x:c r="K90" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L90" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H90" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I90" s="16"/>
+      <x:c r="M90" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N90" s="20"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="11" t="str">
@@ -3004,19 +4323,34 @@
       <x:c r="D91" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E91" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F91" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E91" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F91" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G91" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H91" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I91" s="16" t="n">
+        <x:v>5.27</x:v>
+      </x:c>
+      <x:c r="H91" s="18" t="n">
+        <x:v>13.48</x:v>
+      </x:c>
+      <x:c r="I91" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J91" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K91" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L91" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M91" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N91" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3033,19 +4367,34 @@
       <x:c r="D92" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E92" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F92" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E92" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F92" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G92" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H92" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I92" s="16" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H92" s="18" t="n">
+        <x:v>8.82</x:v>
+      </x:c>
+      <x:c r="I92" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J92" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K92" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L92" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M92" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N92" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3062,19 +4411,34 @@
       <x:c r="D93" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E93" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F93" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E93" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F93" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G93" s="16" t="n">
+        <x:v>4.94</x:v>
+      </x:c>
+      <x:c r="H93" s="18" t="n">
+        <x:v>9.06</x:v>
+      </x:c>
+      <x:c r="I93" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J93" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K93" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L93" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H93" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I93" s="16" t="n">
+      <x:c r="M93" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N93" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3091,19 +4455,34 @@
       <x:c r="D94" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E94" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F94" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E94" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F94" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G94" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H94" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I94" s="16" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="H94" s="18" t="n">
+        <x:v>9.55</x:v>
+      </x:c>
+      <x:c r="I94" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J94" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K94" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L94" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M94" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N94" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3120,19 +4499,34 @@
       <x:c r="D95" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E95" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F95" s="16" t="n">
+      <x:c r="E95" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F95" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G95" s="16" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H95" s="18" t="n">
+        <x:v>6.11</x:v>
+      </x:c>
+      <x:c r="I95" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J95" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K95" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G95" s="16" t="n">
+      <x:c r="L95" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H95" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I95" s="16" t="n">
+      <x:c r="M95" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N95" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3149,19 +4543,34 @@
       <x:c r="D96" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E96" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F96" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E96" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F96" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G96" s="16" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="H96" s="18" t="n">
+        <x:v>7.94</x:v>
+      </x:c>
+      <x:c r="I96" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J96" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K96" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L96" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H96" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I96" s="16" t="n">
+      <x:c r="M96" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N96" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3178,19 +4587,34 @@
       <x:c r="D97" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E97" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F97" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E97" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F97" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G97" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H97" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I97" s="16" t="n">
+        <x:v>1.62</x:v>
+      </x:c>
+      <x:c r="H97" s="18" t="n">
+        <x:v>9.55</x:v>
+      </x:c>
+      <x:c r="I97" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J97" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K97" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L97" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M97" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N97" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3207,19 +4631,34 @@
       <x:c r="D98" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E98" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F98" s="16" t="n">
+      <x:c r="E98" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F98" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G98" s="16" t="n">
+        <x:v>4.84</x:v>
+      </x:c>
+      <x:c r="H98" s="18" t="n">
+        <x:v>13.19</x:v>
+      </x:c>
+      <x:c r="I98" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J98" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K98" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G98" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H98" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I98" s="16" t="n">
+      <x:c r="L98" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M98" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N98" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3236,17 +4675,32 @@
       <x:c r="D99" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E99" s="16"/>
-      <x:c r="F99" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E99" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F99" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G99" s="16" t="n">
+        <x:v>2.92</x:v>
+      </x:c>
+      <x:c r="H99" s="18" t="n">
+        <x:v>10.44</x:v>
+      </x:c>
+      <x:c r="I99" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J99" s="20"/>
+      <x:c r="K99" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L99" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H99" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I99" s="16" t="n">
+      <x:c r="M99" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N99" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3263,19 +4717,34 @@
       <x:c r="D100" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E100" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F100" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E100" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F100" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G100" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H100" s="16" t="n">
+        <x:v>15.71</x:v>
+      </x:c>
+      <x:c r="H100" s="18" t="n">
+        <x:v>26.48</x:v>
+      </x:c>
+      <x:c r="I100" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J100" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K100" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L100" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M100" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I100" s="16" t="n">
+      <x:c r="N100" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3292,19 +4761,34 @@
       <x:c r="D101" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E101" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F101" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E101" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F101" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G101" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H101" s="16" t="n">
+        <x:v>2.58</x:v>
+      </x:c>
+      <x:c r="H101" s="18" t="n">
+        <x:v>7.45</x:v>
+      </x:c>
+      <x:c r="I101" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J101" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K101" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L101" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M101" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I101" s="16" t="n">
+      <x:c r="N101" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3321,17 +4805,32 @@
       <x:c r="D102" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E102" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F102" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G102" s="16"/>
-      <x:c r="H102" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I102" s="16" t="n">
+      <x:c r="E102" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F102" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G102" s="16" t="n">
+        <x:v>17.65</x:v>
+      </x:c>
+      <x:c r="H102" s="18" t="n">
+        <x:v>21.9</x:v>
+      </x:c>
+      <x:c r="I102" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J102" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K102" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L102" s="20"/>
+      <x:c r="M102" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N102" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3348,19 +4847,34 @@
       <x:c r="D103" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E103" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F103" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E103" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F103" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G103" s="16" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="H103" s="18" t="n">
+        <x:v>16.1</x:v>
+      </x:c>
+      <x:c r="I103" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J103" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K103" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L103" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H103" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I103" s="16" t="n">
+      <x:c r="M103" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N103" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3377,19 +4891,34 @@
       <x:c r="D104" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E104" s="16" t="n">
+      <x:c r="E104" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F104" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G104" s="16" t="n">
+        <x:v>5.46</x:v>
+      </x:c>
+      <x:c r="H104" s="18" t="n">
+        <x:v>13.61</x:v>
+      </x:c>
+      <x:c r="I104" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J104" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F104" s="16" t="n">
+      <x:c r="K104" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G104" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H104" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I104" s="16" t="n">
+      <x:c r="L104" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M104" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N104" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3406,19 +4935,34 @@
       <x:c r="D105" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E105" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F105" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E105" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F105" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G105" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H105" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I105" s="16" t="n">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="H105" s="18" t="n">
+        <x:v>6.05</x:v>
+      </x:c>
+      <x:c r="I105" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J105" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K105" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L105" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M105" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N105" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3435,17 +4979,32 @@
       <x:c r="D106" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E106" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F106" s="16" t="n">
+      <x:c r="E106" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F106" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G106" s="16" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="H106" s="18" t="n">
+        <x:v>6.03</x:v>
+      </x:c>
+      <x:c r="I106" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J106" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K106" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G106" s="16"/>
-      <x:c r="H106" s="16" t="n">
+      <x:c r="L106" s="20"/>
+      <x:c r="M106" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I106" s="16"/>
+      <x:c r="N106" s="20"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="11" t="str">
@@ -3460,17 +5019,32 @@
       <x:c r="D107" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E107" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F107" s="16"/>
+      <x:c r="E107" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F107" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G107" s="16" t="n">
+        <x:v>3.08</x:v>
+      </x:c>
+      <x:c r="H107" s="18" t="n">
+        <x:v>11.99</x:v>
+      </x:c>
+      <x:c r="I107" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J107" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K107" s="20"/>
+      <x:c r="L107" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H107" s="16" t="n">
+      <x:c r="M107" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I107" s="16" t="n">
+      <x:c r="N107" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3487,19 +5061,34 @@
       <x:c r="D108" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E108" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F108" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E108" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F108" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G108" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H108" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I108" s="16" t="n">
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="H108" s="18" t="n">
+        <x:v>8.41</x:v>
+      </x:c>
+      <x:c r="I108" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J108" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K108" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L108" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M108" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N108" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3516,19 +5105,34 @@
       <x:c r="D109" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E109" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F109" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E109" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F109" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G109" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H109" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I109" s="16"/>
+        <x:v>2.66</x:v>
+      </x:c>
+      <x:c r="H109" s="18" t="n">
+        <x:v>7.51</x:v>
+      </x:c>
+      <x:c r="I109" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J109" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K109" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L109" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M109" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N109" s="20"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="11" t="str">
@@ -3543,19 +5147,34 @@
       <x:c r="D110" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E110" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F110" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E110" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F110" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G110" s="16" t="n">
+        <x:v>0.91</x:v>
+      </x:c>
+      <x:c r="H110" s="18" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="I110" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J110" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K110" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L110" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H110" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I110" s="16" t="n">
+      <x:c r="M110" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N110" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3572,19 +5191,34 @@
       <x:c r="D111" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E111" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F111" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E111" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F111" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G111" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H111" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I111" s="16" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="H111" s="18" t="n">
+        <x:v>12.79</x:v>
+      </x:c>
+      <x:c r="I111" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J111" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K111" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L111" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M111" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N111" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3601,19 +5235,34 @@
       <x:c r="D112" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E112" s="16" t="n">
+      <x:c r="E112" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F112" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G112" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H112" s="18" t="n">
+        <x:v>18.65</x:v>
+      </x:c>
+      <x:c r="I112" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J112" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F112" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G112" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H112" s="16" t="n">
+      <x:c r="K112" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L112" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M112" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I112" s="16" t="n">
+      <x:c r="N112" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3630,19 +5279,34 @@
       <x:c r="D113" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E113" s="16" t="n">
+      <x:c r="E113" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F113" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G113" s="16" t="n">
+        <x:v>12.26</x:v>
+      </x:c>
+      <x:c r="H113" s="18" t="n">
+        <x:v>16.79</x:v>
+      </x:c>
+      <x:c r="I113" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J113" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F113" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G113" s="16" t="n">
+      <x:c r="K113" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L113" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H113" s="16" t="n">
+      <x:c r="M113" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I113" s="16" t="n">
+      <x:c r="N113" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -3659,19 +5323,34 @@
       <x:c r="D114" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E114" s="16" t="n">
+      <x:c r="E114" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F114" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G114" s="16" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="H114" s="18" t="n">
+        <x:v>6.62</x:v>
+      </x:c>
+      <x:c r="I114" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J114" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F114" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G114" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H114" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I114" s="16" t="n">
+      <x:c r="K114" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L114" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M114" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N114" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3688,20 +5367,35 @@
       <x:c r="D115" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E115" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F115" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E115" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F115" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G115" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H115" s="16" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H115" s="18" t="n">
+        <x:v>6.09</x:v>
+      </x:c>
+      <x:c r="I115" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J115" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K115" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L115" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M115" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I115" s="16" t="n">
-        <x:v>11</x:v>
+      <x:c r="N115" s="20" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -3717,17 +5411,32 @@
       <x:c r="D116" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E116" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F116" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E116" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F116" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G116" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H116" s="16"/>
-      <x:c r="I116" s="16" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="H116" s="18" t="n">
+        <x:v>6.58</x:v>
+      </x:c>
+      <x:c r="I116" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J116" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K116" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L116" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M116" s="20"/>
+      <x:c r="N116" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3744,19 +5453,34 @@
       <x:c r="D117" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E117" s="16" t="n">
+      <x:c r="E117" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F117" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G117" s="16" t="n">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="H117" s="18" t="n">
+        <x:v>13.37</x:v>
+      </x:c>
+      <x:c r="I117" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J117" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F117" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G117" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H117" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I117" s="16" t="n">
+      <x:c r="K117" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L117" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M117" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N117" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3773,19 +5497,34 @@
       <x:c r="D118" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E118" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F118" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E118" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F118" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G118" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H118" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I118" s="16" t="n">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="H118" s="18" t="n">
+        <x:v>6.42</x:v>
+      </x:c>
+      <x:c r="I118" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J118" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K118" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L118" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M118" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N118" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -3802,19 +5541,34 @@
       <x:c r="D119" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E119" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F119" s="16" t="n">
+      <x:c r="E119" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F119" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G119" s="16" t="n">
+        <x:v>3.59</x:v>
+      </x:c>
+      <x:c r="H119" s="18" t="n">
+        <x:v>12.34</x:v>
+      </x:c>
+      <x:c r="I119" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J119" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K119" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G119" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H119" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I119" s="16" t="n">
+      <x:c r="L119" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M119" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N119" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -3831,19 +5585,34 @@
       <x:c r="D120" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E120" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F120" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E120" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F120" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G120" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H120" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I120" s="16" t="n">
+        <x:v>5.3</x:v>
+      </x:c>
+      <x:c r="H120" s="18" t="n">
+        <x:v>13.5</x:v>
+      </x:c>
+      <x:c r="I120" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J120" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K120" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L120" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M120" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N120" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3860,17 +5629,32 @@
       <x:c r="D121" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E121" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F121" s="16"/>
+      <x:c r="E121" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F121" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G121" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H121" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I121" s="16" t="n">
+        <x:v>4.97</x:v>
+      </x:c>
+      <x:c r="H121" s="18" t="n">
+        <x:v>9.08</x:v>
+      </x:c>
+      <x:c r="I121" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J121" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K121" s="20"/>
+      <x:c r="L121" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M121" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N121" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3887,17 +5671,32 @@
       <x:c r="D122" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E122" s="16"/>
-      <x:c r="F122" s="16" t="n">
+      <x:c r="E122" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F122" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G122" s="16" t="n">
+        <x:v>6.93</x:v>
+      </x:c>
+      <x:c r="H122" s="18" t="n">
+        <x:v>10.41</x:v>
+      </x:c>
+      <x:c r="I122" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J122" s="20"/>
+      <x:c r="K122" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G122" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H122" s="16" t="n">
+      <x:c r="L122" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M122" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I122" s="16" t="n">
+      <x:c r="N122" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -3914,19 +5713,34 @@
       <x:c r="D123" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E123" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F123" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E123" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F123" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G123" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H123" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I123" s="16" t="n">
+        <x:v>5.46</x:v>
+      </x:c>
+      <x:c r="H123" s="18" t="n">
+        <x:v>13.61</x:v>
+      </x:c>
+      <x:c r="I123" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J123" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K123" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L123" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M123" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N123" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3943,19 +5757,34 @@
       <x:c r="D124" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E124" s="16" t="n">
+      <x:c r="E124" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F124" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G124" s="16" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="H124" s="18" t="n">
+        <x:v>5.91</x:v>
+      </x:c>
+      <x:c r="I124" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J124" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F124" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G124" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H124" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I124" s="16" t="n">
+      <x:c r="K124" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L124" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M124" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N124" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -3972,19 +5801,34 @@
       <x:c r="D125" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E125" s="16" t="n">
+      <x:c r="E125" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F125" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G125" s="16" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="H125" s="18" t="n">
+        <x:v>9.22</x:v>
+      </x:c>
+      <x:c r="I125" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J125" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F125" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G125" s="16" t="n">
+      <x:c r="K125" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L125" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H125" s="16" t="n">
+      <x:c r="M125" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I125" s="16" t="n">
+      <x:c r="N125" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4001,19 +5845,34 @@
       <x:c r="D126" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E126" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F126" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E126" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F126" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G126" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H126" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I126" s="16" t="n">
+        <x:v>6.16</x:v>
+      </x:c>
+      <x:c r="H126" s="18" t="n">
+        <x:v>14.09</x:v>
+      </x:c>
+      <x:c r="I126" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J126" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K126" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L126" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M126" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N126" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4030,19 +5889,34 @@
       <x:c r="D127" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E127" s="16" t="n">
+      <x:c r="E127" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F127" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G127" s="16" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="H127" s="18" t="n">
+        <x:v>10.65</x:v>
+      </x:c>
+      <x:c r="I127" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J127" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F127" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G127" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H127" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I127" s="16" t="n">
+      <x:c r="K127" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L127" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M127" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N127" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4059,19 +5933,34 @@
       <x:c r="D128" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E128" s="16" t="n">
+      <x:c r="E128" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F128" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G128" s="16" t="n">
+        <x:v>12.51</x:v>
+      </x:c>
+      <x:c r="H128" s="18" t="n">
+        <x:v>14.21</x:v>
+      </x:c>
+      <x:c r="I128" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J128" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F128" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G128" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H128" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I128" s="16" t="n">
+      <x:c r="K128" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L128" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M128" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N128" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4088,19 +5977,34 @@
       <x:c r="D129" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E129" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F129" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E129" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F129" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G129" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H129" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I129" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="H129" s="18" t="n">
+        <x:v>10.41</x:v>
+      </x:c>
+      <x:c r="I129" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J129" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K129" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L129" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M129" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N129" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4117,19 +6021,34 @@
       <x:c r="D130" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E130" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F130" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E130" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F130" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G130" s="16" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H130" s="18" t="n">
+        <x:v>6.04</x:v>
+      </x:c>
+      <x:c r="I130" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J130" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K130" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L130" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H130" s="16" t="n">
+      <x:c r="M130" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I130" s="16" t="n">
+      <x:c r="N130" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4146,19 +6065,34 @@
       <x:c r="D131" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E131" s="16" t="n">
+      <x:c r="E131" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F131" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G131" s="16" t="n">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="H131" s="18" t="n">
+        <x:v>7.23</x:v>
+      </x:c>
+      <x:c r="I131" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J131" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F131" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G131" s="16" t="n">
+      <x:c r="K131" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L131" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H131" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I131" s="16" t="n">
+      <x:c r="M131" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N131" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4175,19 +6109,34 @@
       <x:c r="D132" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E132" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F132" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E132" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F132" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G132" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H132" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I132" s="16" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="H132" s="18" t="n">
+        <x:v>8.59</x:v>
+      </x:c>
+      <x:c r="I132" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J132" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K132" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L132" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M132" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N132" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4204,19 +6153,34 @@
       <x:c r="D133" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E133" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F133" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E133" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F133" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G133" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H133" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I133" s="16" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H133" s="18" t="n">
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="I133" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J133" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K133" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L133" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M133" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N133" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -4233,17 +6197,32 @@
       <x:c r="D134" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E134" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F134" s="16" t="n">
+      <x:c r="E134" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F134" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G134" s="16" t="n">
+        <x:v>4.64</x:v>
+      </x:c>
+      <x:c r="H134" s="18" t="n">
+        <x:v>11.61</x:v>
+      </x:c>
+      <x:c r="I134" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J134" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K134" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G134" s="16" t="n">
+      <x:c r="L134" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H134" s="16"/>
-      <x:c r="I134" s="16" t="n">
+      <x:c r="M134" s="20"/>
+      <x:c r="N134" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4260,19 +6239,34 @@
       <x:c r="D135" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E135" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F135" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E135" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F135" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G135" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H135" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I135" s="16" t="n">
+        <x:v>9.21</x:v>
+      </x:c>
+      <x:c r="H135" s="18" t="n">
+        <x:v>14.71</x:v>
+      </x:c>
+      <x:c r="I135" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J135" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K135" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L135" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M135" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N135" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4289,17 +6283,32 @@
       <x:c r="D136" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E136" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F136" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E136" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F136" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G136" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H136" s="16"/>
-      <x:c r="I136" s="16" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H136" s="18" t="n">
+        <x:v>6.07</x:v>
+      </x:c>
+      <x:c r="I136" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J136" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K136" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L136" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M136" s="20"/>
+      <x:c r="N136" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4316,19 +6325,34 @@
       <x:c r="D137" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E137" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F137" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E137" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F137" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G137" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H137" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I137" s="16" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="H137" s="18" t="n">
+        <x:v>6.23</x:v>
+      </x:c>
+      <x:c r="I137" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J137" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K137" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L137" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M137" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N137" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4345,17 +6369,32 @@
       <x:c r="D138" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E138" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F138" s="16" t="n">
+      <x:c r="E138" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F138" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G138" s="16" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="H138" s="18" t="n">
+        <x:v>8.71</x:v>
+      </x:c>
+      <x:c r="I138" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J138" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K138" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G138" s="16"/>
-      <x:c r="H138" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I138" s="16" t="n">
+      <x:c r="L138" s="20"/>
+      <x:c r="M138" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N138" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4372,19 +6411,34 @@
       <x:c r="D139" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E139" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F139" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E139" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F139" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G139" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H139" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I139" s="16" t="n">
+        <x:v>1.63</x:v>
+      </x:c>
+      <x:c r="H139" s="18" t="n">
+        <x:v>11.01</x:v>
+      </x:c>
+      <x:c r="I139" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J139" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K139" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L139" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M139" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N139" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4401,19 +6455,34 @@
       <x:c r="D140" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E140" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F140" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E140" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F140" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G140" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H140" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I140" s="16" t="n">
+        <x:v>6.35</x:v>
+      </x:c>
+      <x:c r="H140" s="18" t="n">
+        <x:v>12.77</x:v>
+      </x:c>
+      <x:c r="I140" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J140" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K140" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L140" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M140" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N140" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4430,17 +6499,32 @@
       <x:c r="D141" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E141" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F141" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E141" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F141" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G141" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H141" s="16"/>
-      <x:c r="I141" s="16" t="n">
+        <x:v>1.31</x:v>
+      </x:c>
+      <x:c r="H141" s="18" t="n">
+        <x:v>6.59</x:v>
+      </x:c>
+      <x:c r="I141" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J141" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K141" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L141" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M141" s="20"/>
+      <x:c r="N141" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -4457,19 +6541,34 @@
       <x:c r="D142" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E142" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F142" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E142" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F142" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G142" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H142" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I142" s="16" t="n">
+        <x:v>2.54</x:v>
+      </x:c>
+      <x:c r="H142" s="18" t="n">
+        <x:v>7.43</x:v>
+      </x:c>
+      <x:c r="I142" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J142" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K142" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L142" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M142" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N142" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4486,17 +6585,32 @@
       <x:c r="D143" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E143" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F143" s="16" t="n">
+      <x:c r="E143" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F143" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G143" s="16" t="n">
+        <x:v>3.86</x:v>
+      </x:c>
+      <x:c r="H143" s="18" t="n">
+        <x:v>8.32</x:v>
+      </x:c>
+      <x:c r="I143" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J143" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K143" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G143" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H143" s="16"/>
-      <x:c r="I143" s="16" t="n">
+      <x:c r="L143" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M143" s="20"/>
+      <x:c r="N143" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4513,19 +6627,34 @@
       <x:c r="D144" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E144" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F144" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E144" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F144" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G144" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H144" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I144" s="16" t="n">
+        <x:v>8.99</x:v>
+      </x:c>
+      <x:c r="H144" s="18" t="n">
+        <x:v>11.81</x:v>
+      </x:c>
+      <x:c r="I144" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J144" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K144" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L144" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M144" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N144" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4542,19 +6671,34 @@
       <x:c r="D145" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E145" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F145" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E145" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F145" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G145" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H145" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I145" s="16" t="n">
+        <x:v>2.58</x:v>
+      </x:c>
+      <x:c r="H145" s="18" t="n">
+        <x:v>7.45</x:v>
+      </x:c>
+      <x:c r="I145" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J145" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K145" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L145" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M145" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N145" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -4571,19 +6715,34 @@
       <x:c r="D146" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E146" s="16" t="n">
+      <x:c r="E146" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F146" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G146" s="16" t="n">
+        <x:v>4.88</x:v>
+      </x:c>
+      <x:c r="H146" s="18" t="n">
+        <x:v>9.02</x:v>
+      </x:c>
+      <x:c r="I146" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J146" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F146" s="16" t="n">
+      <x:c r="K146" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G146" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H146" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I146" s="16" t="n">
+      <x:c r="L146" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M146" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N146" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4600,17 +6759,32 @@
       <x:c r="D147" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E147" s="16"/>
-      <x:c r="F147" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E147" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F147" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G147" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H147" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I147" s="16" t="n">
+        <x:v>4.64</x:v>
+      </x:c>
+      <x:c r="H147" s="18" t="n">
+        <x:v>11.61</x:v>
+      </x:c>
+      <x:c r="I147" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J147" s="20"/>
+      <x:c r="K147" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L147" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M147" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N147" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -4627,19 +6801,34 @@
       <x:c r="D148" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E148" s="16" t="n">
+      <x:c r="E148" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F148" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G148" s="16" t="n">
+        <x:v>3.81</x:v>
+      </x:c>
+      <x:c r="H148" s="18" t="n">
+        <x:v>8.29</x:v>
+      </x:c>
+      <x:c r="I148" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J148" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F148" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G148" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H148" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I148" s="16" t="n">
+      <x:c r="K148" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L148" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M148" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N148" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4656,17 +6845,32 @@
       <x:c r="D149" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E149" s="16"/>
-      <x:c r="F149" s="16" t="n">
+      <x:c r="E149" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F149" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G149" s="16" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="H149" s="18" t="n">
+        <x:v>19.32</x:v>
+      </x:c>
+      <x:c r="I149" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J149" s="20"/>
+      <x:c r="K149" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G149" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H149" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I149" s="16" t="n">
+      <x:c r="L149" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M149" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N149" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -4683,19 +6887,34 @@
       <x:c r="D150" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E150" s="16" t="n">
+      <x:c r="E150" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F150" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G150" s="16" t="n">
+        <x:v>12.44</x:v>
+      </x:c>
+      <x:c r="H150" s="18" t="n">
+        <x:v>24.26</x:v>
+      </x:c>
+      <x:c r="I150" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J150" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F150" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G150" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H150" s="16" t="n">
+      <x:c r="K150" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L150" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M150" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I150" s="16" t="n">
+      <x:c r="N150" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4712,19 +6931,34 @@
       <x:c r="D151" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E151" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F151" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E151" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F151" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G151" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H151" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I151" s="16" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="H151" s="18" t="n">
+        <x:v>12.91</x:v>
+      </x:c>
+      <x:c r="I151" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J151" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K151" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L151" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M151" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N151" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -4741,19 +6975,34 @@
       <x:c r="D152" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E152" s="16" t="n">
+      <x:c r="E152" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F152" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G152" s="16" t="n">
+        <x:v>1.22</x:v>
+      </x:c>
+      <x:c r="H152" s="18" t="n">
+        <x:v>16.63</x:v>
+      </x:c>
+      <x:c r="I152" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J152" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F152" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G152" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H152" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I152" s="16" t="n">
+      <x:c r="K152" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L152" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M152" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N152" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4770,19 +7019,34 @@
       <x:c r="D153" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E153" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F153" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E153" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F153" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G153" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H153" s="16" t="n">
+        <x:v>1.28</x:v>
+      </x:c>
+      <x:c r="H153" s="18" t="n">
+        <x:v>9.32</x:v>
+      </x:c>
+      <x:c r="I153" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J153" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K153" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L153" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M153" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I153" s="16" t="n">
+      <x:c r="N153" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4799,19 +7063,34 @@
       <x:c r="D154" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E154" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F154" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E154" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F154" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G154" s="16" t="n">
+        <x:v>4.31</x:v>
+      </x:c>
+      <x:c r="H154" s="18" t="n">
+        <x:v>18.73</x:v>
+      </x:c>
+      <x:c r="I154" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J154" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K154" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L154" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H154" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I154" s="16" t="n">
+      <x:c r="M154" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N154" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4828,19 +7107,34 @@
       <x:c r="D155" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E155" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F155" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E155" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F155" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G155" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H155" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I155" s="16" t="n">
+        <x:v>14.62</x:v>
+      </x:c>
+      <x:c r="H155" s="18" t="n">
+        <x:v>28.49</x:v>
+      </x:c>
+      <x:c r="I155" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J155" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K155" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L155" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M155" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N155" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4857,19 +7151,34 @@
       <x:c r="D156" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E156" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F156" s="16" t="n">
+      <x:c r="E156" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F156" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G156" s="16" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="H156" s="18" t="n">
+        <x:v>6.18</x:v>
+      </x:c>
+      <x:c r="I156" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J156" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K156" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G156" s="16" t="n">
+      <x:c r="L156" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H156" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I156" s="16" t="n">
+      <x:c r="M156" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N156" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4886,19 +7195,34 @@
       <x:c r="D157" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E157" s="16" t="n">
+      <x:c r="E157" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F157" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G157" s="16" t="n">
+        <x:v>5.18</x:v>
+      </x:c>
+      <x:c r="H157" s="18" t="n">
+        <x:v>9.22</x:v>
+      </x:c>
+      <x:c r="I157" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J157" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F157" s="16" t="n">
+      <x:c r="K157" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G157" s="16" t="n">
+      <x:c r="L157" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H157" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I157" s="16" t="n">
+      <x:c r="M157" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N157" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -4915,19 +7239,34 @@
       <x:c r="D158" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E158" s="16" t="n">
+      <x:c r="E158" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F158" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G158" s="16" t="n">
+        <x:v>5.33</x:v>
+      </x:c>
+      <x:c r="H158" s="18" t="n">
+        <x:v>9.32</x:v>
+      </x:c>
+      <x:c r="I158" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J158" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F158" s="16" t="n">
+      <x:c r="K158" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G158" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H158" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I158" s="16" t="n">
+      <x:c r="L158" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M158" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N158" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4944,19 +7283,34 @@
       <x:c r="D159" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E159" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F159" s="16" t="n">
+      <x:c r="E159" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F159" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G159" s="16" t="n">
+        <x:v>16.1</x:v>
+      </x:c>
+      <x:c r="H159" s="18" t="n">
+        <x:v>16.65</x:v>
+      </x:c>
+      <x:c r="I159" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J159" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K159" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G159" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H159" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I159" s="16" t="n">
+      <x:c r="L159" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M159" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N159" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4973,19 +7327,34 @@
       <x:c r="D160" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E160" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F160" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E160" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F160" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G160" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H160" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I160" s="16" t="n">
+        <x:v>4.71</x:v>
+      </x:c>
+      <x:c r="H160" s="18" t="n">
+        <x:v>21.75</x:v>
+      </x:c>
+      <x:c r="I160" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J160" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K160" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L160" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M160" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N160" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5002,19 +7371,34 @@
       <x:c r="D161" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E161" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F161" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E161" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F161" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G161" s="16" t="n">
+        <x:v>1.79</x:v>
+      </x:c>
+      <x:c r="H161" s="18" t="n">
+        <x:v>6.92</x:v>
+      </x:c>
+      <x:c r="I161" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J161" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K161" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L161" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H161" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I161" s="16" t="n">
+      <x:c r="M161" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N161" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5031,19 +7415,34 @@
       <x:c r="D162" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E162" s="16" t="n">
+      <x:c r="E162" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F162" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G162" s="16" t="n">
+        <x:v>0.89</x:v>
+      </x:c>
+      <x:c r="H162" s="18" t="n">
+        <x:v>9.06</x:v>
+      </x:c>
+      <x:c r="I162" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J162" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F162" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G162" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H162" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I162" s="16" t="n">
+      <x:c r="K162" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L162" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M162" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N162" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5060,19 +7459,34 @@
       <x:c r="D163" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E163" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F163" s="16" t="n">
+      <x:c r="E163" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F163" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G163" s="16" t="n">
+        <x:v>1.26</x:v>
+      </x:c>
+      <x:c r="H163" s="18" t="n">
+        <x:v>9.31</x:v>
+      </x:c>
+      <x:c r="I163" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J163" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K163" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G163" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H163" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I163" s="16" t="n">
+      <x:c r="L163" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M163" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N163" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -5089,17 +7503,32 @@
       <x:c r="D164" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E164" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F164" s="16"/>
+      <x:c r="E164" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F164" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
       <x:c r="G164" s="16" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H164" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I164" s="16" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="H164" s="18" t="n">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="I164" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J164" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K164" s="20"/>
+      <x:c r="L164" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M164" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N164" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5116,19 +7545,34 @@
       <x:c r="D165" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E165" s="16" t="n">
+      <x:c r="E165" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F165" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G165" s="16" t="n">
+        <x:v>0.77</x:v>
+      </x:c>
+      <x:c r="H165" s="18" t="n">
+        <x:v>16.32</x:v>
+      </x:c>
+      <x:c r="I165" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J165" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F165" s="16" t="n">
+      <x:c r="K165" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G165" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H165" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I165" s="16" t="n">
+      <x:c r="L165" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M165" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N165" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -5145,19 +7589,34 @@
       <x:c r="D166" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E166" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F166" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E166" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F166" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G166" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H166" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I166" s="16" t="n">
+        <x:v>5.25</x:v>
+      </x:c>
+      <x:c r="H166" s="18" t="n">
+        <x:v>9.27</x:v>
+      </x:c>
+      <x:c r="I166" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J166" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K166" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L166" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M166" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N166" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5174,19 +7633,34 @@
       <x:c r="D167" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E167" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F167" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E167" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F167" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G167" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H167" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I167" s="16" t="n">
+        <x:v>1.27</x:v>
+      </x:c>
+      <x:c r="H167" s="18" t="n">
+        <x:v>10.76</x:v>
+      </x:c>
+      <x:c r="I167" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J167" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K167" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L167" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M167" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N167" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5203,17 +7677,32 @@
       <x:c r="D168" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E168" s="16"/>
-      <x:c r="F168" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E168" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F168" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G168" s="16" t="n">
+        <x:v>0.51</x:v>
+      </x:c>
+      <x:c r="H168" s="18" t="n">
+        <x:v>6.05</x:v>
+      </x:c>
+      <x:c r="I168" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J168" s="20"/>
+      <x:c r="K168" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L168" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H168" s="16" t="n">
+      <x:c r="M168" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I168" s="16" t="n">
+      <x:c r="N168" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5230,19 +7719,34 @@
       <x:c r="D169" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E169" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F169" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E169" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F169" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G169" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H169" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I169" s="16" t="n">
+        <x:v>2.78</x:v>
+      </x:c>
+      <x:c r="H169" s="18" t="n">
+        <x:v>7.59</x:v>
+      </x:c>
+      <x:c r="I169" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J169" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K169" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L169" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M169" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N169" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5259,17 +7763,32 @@
       <x:c r="D170" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E170" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F170" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G170" s="16"/>
-      <x:c r="H170" s="16" t="n">
+      <x:c r="E170" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F170" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G170" s="16" t="n">
+        <x:v>5.61</x:v>
+      </x:c>
+      <x:c r="H170" s="18" t="n">
+        <x:v>9.51</x:v>
+      </x:c>
+      <x:c r="I170" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J170" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K170" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L170" s="20"/>
+      <x:c r="M170" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I170" s="16"/>
+      <x:c r="N170" s="20"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="11" t="str">
@@ -5284,19 +7803,34 @@
       <x:c r="D171" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E171" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F171" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E171" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F171" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G171" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H171" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I171" s="16" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="H171" s="18" t="n">
+        <x:v>8.75</x:v>
+      </x:c>
+      <x:c r="I171" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J171" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K171" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L171" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M171" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N171" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -5313,19 +7847,34 @@
       <x:c r="D172" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E172" s="16" t="n">
+      <x:c r="E172" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F172" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G172" s="16" t="n">
+        <x:v>0.89</x:v>
+      </x:c>
+      <x:c r="H172" s="18" t="n">
+        <x:v>10.51</x:v>
+      </x:c>
+      <x:c r="I172" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J172" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F172" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G172" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H172" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I172" s="16"/>
+      <x:c r="K172" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L172" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M172" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N172" s="20"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="11" t="str">
@@ -5340,19 +7889,34 @@
       <x:c r="D173" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E173" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F173" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E173" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F173" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G173" s="16" t="n">
+        <x:v>1.03</x:v>
+      </x:c>
+      <x:c r="H173" s="18" t="n">
+        <x:v>10.6</x:v>
+      </x:c>
+      <x:c r="I173" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J173" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K173" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L173" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H173" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I173" s="16" t="n">
+      <x:c r="M173" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N173" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5369,17 +7933,32 @@
       <x:c r="D174" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E174" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F174" s="16" t="n">
+      <x:c r="E174" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F174" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G174" s="16" t="n">
+        <x:v>12.13</x:v>
+      </x:c>
+      <x:c r="H174" s="18" t="n">
+        <x:v>18.15</x:v>
+      </x:c>
+      <x:c r="I174" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J174" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K174" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G174" s="16"/>
-      <x:c r="H174" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I174" s="16" t="n">
+      <x:c r="L174" s="20"/>
+      <x:c r="M174" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N174" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5396,19 +7975,34 @@
       <x:c r="D175" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E175" s="16" t="n">
+      <x:c r="E175" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F175" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G175" s="16" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="H175" s="18" t="n">
+        <x:v>8.66</x:v>
+      </x:c>
+      <x:c r="I175" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J175" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F175" s="16" t="n">
+      <x:c r="K175" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G175" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H175" s="16" t="n">
+      <x:c r="L175" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M175" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I175" s="16" t="n">
+      <x:c r="N175" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5425,19 +8019,34 @@
       <x:c r="D176" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E176" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F176" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E176" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F176" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G176" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H176" s="16" t="n">
+        <x:v>1.41</x:v>
+      </x:c>
+      <x:c r="H176" s="18" t="n">
+        <x:v>6.66</x:v>
+      </x:c>
+      <x:c r="I176" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J176" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K176" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L176" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M176" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I176" s="16" t="n">
+      <x:c r="N176" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5454,19 +8063,34 @@
       <x:c r="D177" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E177" s="16" t="n">
+      <x:c r="E177" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F177" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G177" s="16" t="n">
+        <x:v>10.88</x:v>
+      </x:c>
+      <x:c r="H177" s="18" t="n">
+        <x:v>13.1</x:v>
+      </x:c>
+      <x:c r="I177" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J177" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F177" s="16" t="n">
+      <x:c r="K177" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G177" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H177" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I177" s="16" t="n">
+      <x:c r="L177" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M177" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N177" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -5483,17 +8107,32 @@
       <x:c r="D178" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E178" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F178" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G178" s="16"/>
-      <x:c r="H178" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I178" s="16"/>
+      <x:c r="E178" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F178" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G178" s="16" t="n">
+        <x:v>3.66</x:v>
+      </x:c>
+      <x:c r="H178" s="18" t="n">
+        <x:v>21.04</x:v>
+      </x:c>
+      <x:c r="I178" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J178" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K178" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L178" s="20"/>
+      <x:c r="M178" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N178" s="20"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="11" t="str">
@@ -5508,19 +8147,34 @@
       <x:c r="D179" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E179" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F179" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E179" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F179" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G179" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H179" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I179" s="16" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="H179" s="18" t="n">
+        <x:v>9.39</x:v>
+      </x:c>
+      <x:c r="I179" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J179" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K179" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L179" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M179" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N179" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5537,19 +8191,34 @@
       <x:c r="D180" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E180" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F180" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E180" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F180" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G180" s="16" t="n">
+        <x:v>11.48</x:v>
+      </x:c>
+      <x:c r="H180" s="18" t="n">
+        <x:v>26.36</x:v>
+      </x:c>
+      <x:c r="I180" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J180" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K180" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L180" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H180" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I180" s="16" t="n">
+      <x:c r="M180" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N180" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5566,17 +8235,32 @@
       <x:c r="D181" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E181" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F181" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E181" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F181" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G181" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H181" s="16"/>
-      <x:c r="I181" s="16" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="H181" s="18" t="n">
+        <x:v>13.57</x:v>
+      </x:c>
+      <x:c r="I181" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J181" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K181" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L181" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M181" s="20"/>
+      <x:c r="N181" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5593,19 +8277,34 @@
       <x:c r="D182" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E182" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F182" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E182" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F182" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G182" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H182" s="16" t="n">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="H182" s="18" t="n">
+        <x:v>7.91</x:v>
+      </x:c>
+      <x:c r="I182" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J182" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K182" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L182" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M182" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I182" s="16" t="n">
+      <x:c r="N182" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5622,19 +8321,34 @@
       <x:c r="D183" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E183" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F183" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E183" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F183" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G183" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H183" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I183" s="16" t="n">
+        <x:v>15.94</x:v>
+      </x:c>
+      <x:c r="H183" s="18" t="n">
+        <x:v>26.64</x:v>
+      </x:c>
+      <x:c r="I183" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J183" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K183" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L183" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M183" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N183" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5651,17 +8365,32 @@
       <x:c r="D184" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E184" s="16"/>
-      <x:c r="F184" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E184" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F184" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G184" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H184" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I184" s="16" t="n">
+        <x:v>6.55</x:v>
+      </x:c>
+      <x:c r="H184" s="18" t="n">
+        <x:v>14.35</x:v>
+      </x:c>
+      <x:c r="I184" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J184" s="20"/>
+      <x:c r="K184" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L184" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M184" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N184" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5678,19 +8407,34 @@
       <x:c r="D185" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E185" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F185" s="16" t="n">
+      <x:c r="E185" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F185" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G185" s="16" t="n">
+        <x:v>4.71</x:v>
+      </x:c>
+      <x:c r="H185" s="18" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I185" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J185" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K185" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G185" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H185" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I185" s="16" t="n">
+      <x:c r="L185" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M185" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N185" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5707,19 +8451,34 @@
       <x:c r="D186" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E186" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F186" s="16" t="n">
-        <x:v>8</x:v>
+      <x:c r="E186" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F186" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G186" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H186" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I186" s="16" t="n">
+        <x:v>1.19</x:v>
+      </x:c>
+      <x:c r="H186" s="18" t="n">
+        <x:v>16.61</x:v>
+      </x:c>
+      <x:c r="I186" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J186" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K186" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L186" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M186" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N186" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5736,19 +8495,34 @@
       <x:c r="D187" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E187" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F187" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E187" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F187" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G187" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H187" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I187" s="16" t="n">
+        <x:v>5.65</x:v>
+      </x:c>
+      <x:c r="H187" s="18" t="n">
+        <x:v>9.54</x:v>
+      </x:c>
+      <x:c r="I187" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J187" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K187" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L187" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M187" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N187" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5765,19 +8539,34 @@
       <x:c r="D188" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E188" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F188" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E188" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F188" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G188" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H188" s="16" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H188" s="18" t="n">
+        <x:v>6.35</x:v>
+      </x:c>
+      <x:c r="I188" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J188" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K188" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L188" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M188" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I188" s="16" t="n">
+      <x:c r="N188" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5794,17 +8583,32 @@
       <x:c r="D189" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E189" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F189" s="16"/>
+      <x:c r="E189" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F189" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="G189" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H189" s="16" t="n">
+        <x:v>2.24</x:v>
+      </x:c>
+      <x:c r="H189" s="18" t="n">
+        <x:v>14.17</x:v>
+      </x:c>
+      <x:c r="I189" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J189" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K189" s="20"/>
+      <x:c r="L189" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M189" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I189" s="16" t="n">
+      <x:c r="N189" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5821,19 +8625,34 @@
       <x:c r="D190" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E190" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F190" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E190" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F190" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G190" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H190" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I190" s="16" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="H190" s="18" t="n">
+        <x:v>15.47</x:v>
+      </x:c>
+      <x:c r="I190" s="11" t="str">
+        <x:v>En transit</x:v>
+      </x:c>
+      <x:c r="J190" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K190" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L190" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M190" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N190" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5850,19 +8669,34 @@
       <x:c r="D191" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E191" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F191" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E191" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F191" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G191" s="16" t="n">
+        <x:v>2.01</x:v>
+      </x:c>
+      <x:c r="H191" s="18" t="n">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="I191" s="11" t="str">
+        <x:v>Retourné</x:v>
+      </x:c>
+      <x:c r="J191" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K191" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L191" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H191" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I191" s="16" t="n">
+      <x:c r="M191" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N191" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5879,19 +8713,34 @@
       <x:c r="D192" s="11" t="str">
         <x:v>PARCEL_PREMIUM</x:v>
       </x:c>
-      <x:c r="E192" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F192" s="16" t="n">
-        <x:v>10</x:v>
+      <x:c r="E192" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F192" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G192" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H192" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I192" s="16" t="n">
+        <x:v>11.43</x:v>
+      </x:c>
+      <x:c r="H192" s="18" t="n">
+        <x:v>23.57</x:v>
+      </x:c>
+      <x:c r="I192" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J192" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K192" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L192" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M192" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N192" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -5908,19 +8757,34 @@
       <x:c r="D193" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E193" s="16" t="n">
+      <x:c r="E193" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F193" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G193" s="16" t="n">
+        <x:v>5.14</x:v>
+      </x:c>
+      <x:c r="H193" s="18" t="n">
+        <x:v>16.15</x:v>
+      </x:c>
+      <x:c r="I193" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J193" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F193" s="16" t="n">
+      <x:c r="K193" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G193" s="16" t="n">
+      <x:c r="L193" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H193" s="16" t="n">
+      <x:c r="M193" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I193" s="16" t="n">
+      <x:c r="N193" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -5937,19 +8801,34 @@
       <x:c r="D194" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E194" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F194" s="16" t="n">
-        <x:v>7</x:v>
+      <x:c r="E194" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F194" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G194" s="16" t="n">
+        <x:v>5.79</x:v>
+      </x:c>
+      <x:c r="H194" s="18" t="n">
+        <x:v>9.64</x:v>
+      </x:c>
+      <x:c r="I194" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J194" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K194" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L194" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H194" s="16" t="n">
+      <x:c r="M194" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I194" s="16" t="n">
+      <x:c r="N194" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5966,19 +8845,34 @@
       <x:c r="D195" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E195" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F195" s="16" t="n">
+      <x:c r="E195" s="11" t="str">
+        <x:v>Grand</x:v>
+      </x:c>
+      <x:c r="F195" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G195" s="16" t="n">
+        <x:v>8.55</x:v>
+      </x:c>
+      <x:c r="H195" s="18" t="n">
+        <x:v>14.26</x:v>
+      </x:c>
+      <x:c r="I195" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J195" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K195" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G195" s="16" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H195" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I195" s="16" t="n">
+      <x:c r="L195" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M195" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N195" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5995,19 +8889,34 @@
       <x:c r="D196" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E196" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F196" s="16" t="n">
+      <x:c r="E196" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F196" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G196" s="16" t="n">
+        <x:v>0.62</x:v>
+      </x:c>
+      <x:c r="H196" s="18" t="n">
+        <x:v>6.12</x:v>
+      </x:c>
+      <x:c r="I196" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J196" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K196" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G196" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H196" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I196" s="16" t="n">
+      <x:c r="L196" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M196" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N196" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -6024,19 +8933,34 @@
       <x:c r="D197" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E197" s="16" t="n">
+      <x:c r="E197" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F197" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G197" s="16" t="n">
+        <x:v>1.46</x:v>
+      </x:c>
+      <x:c r="H197" s="18" t="n">
+        <x:v>9.44</x:v>
+      </x:c>
+      <x:c r="I197" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J197" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F197" s="16" t="n">
+      <x:c r="K197" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G197" s="16" t="n">
+      <x:c r="L197" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H197" s="16" t="n">
+      <x:c r="M197" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I197" s="16" t="n">
+      <x:c r="N197" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -6053,17 +8977,32 @@
       <x:c r="D198" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E198" s="16"/>
-      <x:c r="F198" s="16" t="n">
-        <x:v>6</x:v>
+      <x:c r="E198" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F198" s="11" t="str">
+        <x:v>Non</x:v>
       </x:c>
       <x:c r="G198" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H198" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I198" s="16" t="n">
+        <x:v>1.38</x:v>
+      </x:c>
+      <x:c r="H198" s="18" t="n">
+        <x:v>6.64</x:v>
+      </x:c>
+      <x:c r="I198" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J198" s="20"/>
+      <x:c r="K198" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L198" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M198" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N198" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6080,19 +9019,34 @@
       <x:c r="D199" s="11" t="str">
         <x:v>PARCEL_EXPRESS</x:v>
       </x:c>
-      <x:c r="E199" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F199" s="16" t="n">
-        <x:v>9</x:v>
+      <x:c r="E199" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F199" s="11" t="str">
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="G199" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H199" s="16" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I199" s="16" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="H199" s="18" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="I199" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J199" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K199" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L199" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M199" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N199" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6109,19 +9063,34 @@
       <x:c r="D200" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E200" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F200" s="16" t="n">
+      <x:c r="E200" s="11" t="str">
+        <x:v>Moyen</x:v>
+      </x:c>
+      <x:c r="F200" s="11" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G200" s="16" t="n">
+        <x:v>2.57</x:v>
+      </x:c>
+      <x:c r="H200" s="18" t="n">
+        <x:v>7.45</x:v>
+      </x:c>
+      <x:c r="I200" s="11" t="str">
+        <x:v>Livré</x:v>
+      </x:c>
+      <x:c r="J200" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K200" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G200" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H200" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I200" s="16" t="n">
+      <x:c r="L200" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M200" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N200" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6138,66 +9107,66 @@
       <x:c r="D201" s="11" t="str">
         <x:v>PARCEL_STANDARD</x:v>
       </x:c>
-      <x:c r="E201" s="16" t="n">
+      <x:c r="E201" s="11" t="str">
+        <x:v>Petit</x:v>
+      </x:c>
+      <x:c r="F201" s="11" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G201" s="16" t="n">
+        <x:v>1.37</x:v>
+      </x:c>
+      <x:c r="H201" s="18" t="n">
+        <x:v>9.38</x:v>
+      </x:c>
+      <x:c r="I201" s="11" t="str">
+        <x:v>Retardé</x:v>
+      </x:c>
+      <x:c r="J201" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F201" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G201" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H201" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I201" s="16" t="n">
+      <x:c r="K201" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L201" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M201" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N201" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E2:E201">
+  <x:conditionalFormatting sqref="J2:J201">
     <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>OR(E2&lt;1,E2&gt;10)</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="1" priority="2">
-      <x:formula>ISBLANK(E2)</x:formula>
+      <x:formula>ISBLANK(J2)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F2:F201">
-    <x:cfRule type="expression" dxfId="2" priority="3">
-      <x:formula>OR(F2&lt;1,F2&gt;10)</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="3" priority="4">
-      <x:formula>ISBLANK(F2)</x:formula>
+  <x:conditionalFormatting sqref="K2:K201">
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>ISBLANK(K2)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G2:G201">
-    <x:cfRule type="expression" dxfId="4" priority="5">
-      <x:formula>OR(G2&lt;1,G2&gt;10)</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="5" priority="6">
-      <x:formula>ISBLANK(G2)</x:formula>
+  <x:conditionalFormatting sqref="L2:L201">
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>ISBLANK(L2)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H2:H201">
-    <x:cfRule type="expression" dxfId="6" priority="7">
-      <x:formula>OR(H2&lt;1,H2&gt;10)</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="7" priority="8">
-      <x:formula>ISBLANK(H2)</x:formula>
+  <x:conditionalFormatting sqref="M2:M201">
+    <x:cfRule type="expression" dxfId="3" priority="4">
+      <x:formula>ISBLANK(M2)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I2:I201">
-    <x:cfRule type="expression" dxfId="8" priority="9">
-      <x:formula>OR(I2&lt;1,I2&gt;10)</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="9" priority="10">
-      <x:formula>ISBLANK(I2)</x:formula>
+  <x:conditionalFormatting sqref="N2:N201">
+    <x:cfRule type="expression" dxfId="4" priority="5">
+      <x:formula>ISBLANK(N2)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81791230542842ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07ab5a941afd4ea6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6206,104 +9175,144 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="68" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="74" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>Dataset</x:v>
-      </x:c>
-      <x:c r="B1" s="20" t="str">
-        <x:v>FastColis Canada - Synthetic Customer Satisfaction Surveys</x:v>
+      <x:c r="A1" s="24" t="str">
+        <x:v>Jeu de données</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>FastColis Canada - Enquêtes fictives de satisfaction</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="18" t="str">
-        <x:v>Rows</x:v>
+      <x:c r="A2" s="22" t="str">
+        <x:v>Nombre de lignes</x:v>
       </x:c>
       <x:c r="B2" t="n">
         <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="18" t="str">
-        <x:v>Period</x:v>
+      <x:c r="A3" s="22" t="str">
+        <x:v>Période</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>01/01/2026 to 30/09/2026</x:v>
+        <x:v>01/01/2026 au 30/09/2026</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str">
-        <x:v>Country</x:v>
+      <x:c r="A4" s="22" t="str">
+        <x:v>Pays</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>Canada</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str">
-        <x:v>Expected rating scale</x:v>
+      <x:c r="A5" s="22" t="str">
+        <x:v>Échelle de satisfaction</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>1 to 10</x:v>
+        <x:v>Notes entières valides de 1 à 10 uniquement</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str">
-        <x:v>Normalization rule</x:v>
+      <x:c r="A6" s="22" t="str">
+        <x:v>Notes hors domaine</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Score on 5 = Score on 10 / 2</x:v>
+        <x:v>Aucune note &lt; 1 ou &gt; 10</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Missing values</x:v>
+      <x:c r="A7" s="22" t="str">
+        <x:v>Valeurs manquantes</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>50 rating cells (~5% of 1000 rating cells)</x:v>
+        <x:v>Les valeurs manquantes d'origine sont conservées</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str">
-        <x:v>Logical duplicates</x:v>
+      <x:c r="A8" s="22" t="str">
+        <x:v>Doublons logiques</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>6 duplicated survey profiles with unique survey_id values</x:v>
+        <x:v>Les doublons logiques présents dans la source sont conservés pour le pipeline de nettoyage</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Outliers</x:v>
+      <x:c r="A9" s="22" t="str">
+        <x:v>Corrections qualité</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>8 intentionally invalid ratings outside the 1-10 scale</x:v>
+        <x:v>8 notes hors domaine corrigées avec une valeur cohérente de 1 à 10</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="str">
-        <x:v>Logical inconsistencies</x:v>
+      <x:c r="A10" s="22" t="str">
+        <x:v>Nouvelles colonnes</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>8 deliberately inconsistent profiles for data-quality testing</x:v>
+        <x:v>taille_colis, fragile, poids_kg, prix_livraison_eur, statut_colis</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="18" t="str">
-        <x:v>Personal data</x:v>
+      <x:c r="A11" s="22" t="str">
+        <x:v>taille_colis</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>No real personal data</x:v>
+        <x:v>Petit, Moyen ou Grand</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="18" t="str">
-        <x:v>Purpose</x:v>
+      <x:c r="A12" s="22" t="str">
+        <x:v>fragile</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>Test ingestion, profiling, cleaning, anomaly detection and score normalization</x:v>
+        <x:v>Oui ou Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>poids_kg</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Poids réaliste cohérent avec la taille du colis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>prix_livraison_eur</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Prix cohérent avec le produit, le poids et la fragilité</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>statut_colis</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Livré, En transit, Retardé ou Retourné</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>Données personnelles</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Aucune donnée personnelle réelle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>Objectif</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Tester ingestion, profiling, qualité, corrélations, nettoyage puis standardisation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
